--- a/data/Class.xlsx
+++ b/data/Class.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,16 +427,6 @@
           <t>skill</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>skill</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>skill</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -446,78 +436,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>uint32</t>
+          <t>repeated uint32</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="4"/>
     <row r="5"/>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13</v>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
@@ -531,7 +498,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -545,7 +512,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -559,7 +526,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
@@ -573,7 +540,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -587,7 +554,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -601,7 +568,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
@@ -610,20 +577,6 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
         <v>1</v>
       </c>
     </row>
